--- a/Result/profitability/1907.xlsx
+++ b/Result/profitability/1907.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2725</v>
+        <v>0.25625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.4725</v>
+        <v>12.59125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0.27375</v>
       </c>
       <c r="N3" t="n">
-        <v>12.44625</v>
+        <v>12.78625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2275</v>
+        <v>0.28125</v>
       </c>
       <c r="N4" t="n">
-        <v>12.68375</v>
+        <v>12.9425</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.73</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1475</v>
+        <v>0.1850000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>11.86625</v>
+        <v>11.9575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.11125</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>11.76</v>
+        <v>12.14125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.005000000000000003</v>
+        <v>-0.002499999999999993</v>
       </c>
       <c r="N7" t="n">
-        <v>12.4525</v>
+        <v>12.5325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02125</v>
+        <v>0.04750000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>12.9075</v>
+        <v>13.0425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19895</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16995</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2901</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>133</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>689</v>
+      </c>
+      <c r="J75" t="n">
+        <v>823</v>
+      </c>
+      <c r="K75" t="n">
+        <v>571</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.615384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7300000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05270758122743691</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
